--- a/etf_holdings/2026-09-24_active_etf_full_holdings_all.xlsx
+++ b/etf_holdings/2026-09-24_active_etf_full_holdings_all.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M46"/>
+  <dimension ref="A1:M96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,17 +486,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:39:33</t>
+          <t>2026-09-24 21:47:14</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00980A/holdings</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -504,7 +504,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2330台積電</t>
+          <t>2330台灣積體電路製造</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -522,16 +522,16 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8.75%1,034,000</t>
+          <t>9.32%753,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8.75%</t>
+          <t>9.32%</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>1034000</v>
+        <v>753000</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -547,17 +547,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-24 21:39:33</t>
+          <t>2026-09-24 21:47:14</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00980A/holdings</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -565,7 +565,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2454聯發科</t>
+          <t>2454聯發科技</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -583,20 +583,20 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7.99%442,000</t>
+          <t>6.39%249,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>7.99%</t>
+          <t>6.39%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>442000</v>
+        <v>249000</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -608,17 +608,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-24 21:39:33</t>
+          <t>2026-09-24 21:47:14</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00980A/holdings</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -626,38 +626,38 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3653健策</t>
+          <t>2059川湖科技</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+7.96%6920</t>
+          <t>-0.32%12350</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+7.96%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>6920</v>
+        <v>12350</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5.23%221,000</t>
+          <t>4.11%67,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.23%</t>
+          <t>4.11%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>221000</v>
+        <v>67000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.39%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -669,17 +669,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-24 21:39:33</t>
+          <t>2026-09-24 21:47:14</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00980A/holdings</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -687,38 +687,38 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2059川湖</t>
+          <t>2308台達電子工業</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-0.32%12350</t>
+          <t>+0.53%1910</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>+0.53%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>12350</v>
+        <v>1910</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.19%123,000</t>
+          <t>3.80%404,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.19%</t>
+          <t>3.80%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>123000</v>
+        <v>404000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -730,17 +730,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-24 21:39:33</t>
+          <t>2026-09-24 21:47:14</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00980A/holdings</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -748,38 +748,38 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3443創意</t>
+          <t>3037欣興電子</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+1.67%8525</t>
+          <t>+2.16%1185</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+1.67%</t>
+          <t>+2.16%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>8525</v>
+        <v>1185</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5.04%173,000</t>
+          <t>3.40%591,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.04%</t>
+          <t>3.40%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>173000</v>
+        <v>591000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -791,17 +791,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-24 21:39:33</t>
+          <t>2026-09-24 21:47:14</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00980A/holdings</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -809,38 +809,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3037欣興</t>
+          <t>2383台光電子材料</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+2.16%1185</t>
+          <t>+0.6%5050</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+2.16%</t>
+          <t>+0.6%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1185</v>
+        <v>5050</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4.90%1,209,000</t>
+          <t>3.38%136,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4.90%</t>
+          <t>3.38%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>1209000</v>
+        <v>136000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -852,17 +852,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-24 21:39:33</t>
+          <t>2026-09-24 21:47:14</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00980A/holdings</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -870,38 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3017奇鋐</t>
+          <t>2408南亞科技</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+2.45%3555</t>
+          <t>-2.33%503</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+2.45%</t>
+          <t>-2.33%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>3555</v>
+        <v>503</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4.58%377,000</t>
+          <t>2.80%1,096,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4.58%</t>
+          <t>2.80%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>377000</v>
+        <v>1096000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -913,17 +913,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-24 21:39:33</t>
+          <t>2026-09-24 21:47:14</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00980A/holdings</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -931,38 +931,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>6223旺矽</t>
+          <t>1303南亞塑膠工業</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-3.65%5415</t>
+          <t>+4.62%238</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-3.65%</t>
+          <t>+4.62%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5415</v>
+        <v>238</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.41%238,000</t>
+          <t>2.72%2,416,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.41%</t>
+          <t>2.72%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>238000</v>
+        <v>2416000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -974,17 +974,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-24 21:39:33</t>
+          <t>2026-09-24 21:47:14</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00980A/holdings</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -992,38 +992,38 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2383台光電</t>
+          <t>3443創意電子</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+0.6%5050</t>
+          <t>+1.67%8525</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+0.6%</t>
+          <t>+1.67%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5050</v>
+        <v>8525</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.92%227,000</t>
+          <t>2.45%59,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.92%</t>
+          <t>2.45%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>227000</v>
+        <v>59000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1035,17 +1035,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-24 21:39:33</t>
+          <t>2026-09-24 21:47:14</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00980A/holdings</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1053,38 +1053,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>2317鴻海精密工業</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+0.53%1910</t>
+          <t>-2.15%250.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+0.53%</t>
+          <t>-2.15%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1910</v>
+        <v>250.5</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.91%598,000</t>
+          <t>2.44%1,921,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.91%</t>
+          <t>2.44%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>598000</v>
+        <v>1921000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1096,17 +1096,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-24 21:39:33</t>
+          <t>2026-09-24 21:47:14</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00980A/holdings</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1114,38 +1114,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2360致茂</t>
+          <t>3017奇鋐科技</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-1.29%2295</t>
+          <t>+2.45%3555</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-1.29%</t>
+          <t>+2.45%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>2295</v>
+        <v>3555</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.69%470,000</t>
+          <t>2.30%134,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.69%</t>
+          <t>2.30%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>470000</v>
+        <v>134000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1157,17 +1157,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-24 21:39:33</t>
+          <t>2026-09-24 21:47:14</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00980A/holdings</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1175,34 +1175,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>5274信 驊</t>
+          <t>2368金像電子（股）公司</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-2.19%19835</t>
+          <t>-3.07%1105</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-3.07%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>19835</v>
+        <v>1105</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.21%47,400</t>
+          <t>2.22%393,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.21%</t>
+          <t>2.22%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>47400</v>
+        <v>393000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1218,17 +1218,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-24 21:39:33</t>
+          <t>2026-09-24 21:47:14</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00980A/holdings</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>6669緯穎</t>
+          <t>3653健策精密工業</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+0.48%2115</t>
+          <t>+7.96%6920</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+0.48%</t>
+          <t>+7.96%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>2115</v>
+        <v>6920</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.17%438,197</t>
+          <t>2.19%69,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3.17%</t>
+          <t>2.19%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>438197</v>
+        <v>69000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1279,17 +1279,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-24 21:39:33</t>
+          <t>2026-09-24 21:47:14</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00980A/holdings</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1303南亞</t>
+          <t>7769鴻勁精密</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+4.62%238</t>
+          <t>-5.1%5670</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+4.62%</t>
+          <t>-5.1%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>238</v>
+        <v>5670</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.95%3,627,000</t>
+          <t>2.16%73,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.95%</t>
+          <t>2.16%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>3627000</v>
+        <v>73000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1340,17 +1340,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-24 21:39:33</t>
+          <t>2026-09-24 21:47:14</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00980A/holdings</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>6187萬 潤</t>
+          <t>3711日月光投資控股</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-0.83%1195</t>
+          <t>+0.87%699</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-0.83%</t>
+          <t>+0.87%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1195</v>
+        <v>699</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.44%596,000</t>
+          <t>2.13%621,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.44%</t>
+          <t>2.13%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>596000</v>
+        <v>621000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1401,17 +1401,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-24 21:39:35</t>
+          <t>2026-09-24 21:47:16</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00980A/holdings</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1419,38 +1419,38 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>6488環球晶</t>
+          <t>5274信驊科技</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-0.21%948</t>
+          <t>-2.19%19835</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>-2.19%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>948</v>
+        <v>19835</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.02%622,000</t>
+          <t>2.04%20,300</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.02%</t>
+          <t>2.04%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>622000</v>
+        <v>20300</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1462,17 +1462,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-24 21:39:35</t>
+          <t>2026-09-24 21:47:16</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00980A/holdings</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>2344華邦電子</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0%2340</t>
+          <t>-0.58%171.5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-0.58%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>2340</v>
+        <v>171.5</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.93%241,000</t>
+          <t>1.96%2,293,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.93%</t>
+          <t>1.96%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>241000</v>
+        <v>2293000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1523,17 +1523,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-24 21:39:35</t>
+          <t>2026-09-24 21:47:16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00980A/holdings</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3044健鼎</t>
+          <t>6223旺矽科技</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-0.92%538</t>
+          <t>-3.65%5415</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-0.92%</t>
+          <t>-3.65%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>538</v>
+        <v>5415</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.90%1,034,000</t>
+          <t>1.84%66,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.90%</t>
+          <t>1.84%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>1034000</v>
+        <v>66000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1584,17 +1584,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-24 21:39:35</t>
+          <t>2026-09-24 21:47:16</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00980A/holdings</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1602,38 +1602,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2881富邦金</t>
+          <t>8299群聯電子</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-1.96%150</t>
+          <t>-4.06%2125</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-1.96%</t>
+          <t>-4.06%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>150</v>
+        <v>2125</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.59%3,104,000</t>
+          <t>1.84%168,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.59%</t>
+          <t>1.84%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>3104000</v>
+        <v>168000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1645,17 +1645,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-24 21:39:35</t>
+          <t>2026-09-24 21:47:16</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00980A/holdings</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>3036文曄</t>
+          <t>6274台燿科技</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+0.49%207</t>
+          <t>+2.4%1495</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>+2.4%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>207</v>
+        <v>1495</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.56%2,208,000</t>
+          <t>1.74%240,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>1.74%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>2208000</v>
+        <v>240000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1706,17 +1706,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-24 21:39:35</t>
+          <t>2026-09-24 21:47:16</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00980A/holdings</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1724,38 +1724,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>3081聯亞光電工業</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+0.26%1895</t>
+          <t>+0.75%2700</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.75%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1895</v>
+        <v>2700</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.47%227,000</t>
+          <t>1.71%128,600</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>1.71%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>227000</v>
+        <v>128600</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1767,17 +1767,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-24 21:39:35</t>
+          <t>2026-09-24 21:47:16</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00980A/holdings</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1785,38 +1785,38 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>6505台塑化</t>
+          <t>2360致茂電子</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-0.11%87.2</t>
+          <t>-1.29%2295</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>-1.29%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>87.2</v>
+        <v>2295</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.46%4,903,000</t>
+          <t>1.70%148,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.70%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>4903000</v>
+        <v>148000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1828,17 +1828,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-24 21:39:35</t>
+          <t>2026-09-24 21:47:16</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00980A/holdings</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1846,38 +1846,38 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3529力旺</t>
+          <t>2382廣達電腦</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-2.27%3230</t>
+          <t>-0.88%338.5</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-2.27%</t>
+          <t>-0.88%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>3230</v>
+        <v>338.5</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.46%132,000</t>
+          <t>1.67%987,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.67%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>132000</v>
+        <v>987000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1889,17 +1889,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-24 21:39:35</t>
+          <t>2026-09-24 21:47:16</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00980A/holdings</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1907,38 +1907,38 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2368金像電</t>
+          <t>2345智邦科技</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-3.07%1105</t>
+          <t>+0.26%1895</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-3.07%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1105</v>
+        <v>1895</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.43%378,000</t>
+          <t>1.63%174,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.43%</t>
+          <t>1.63%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>378000</v>
+        <v>174000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1950,17 +1950,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-24 21:39:35</t>
+          <t>2026-09-24 21:47:16</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00980A/holdings</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1968,38 +1968,38 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>3026禾伸堂</t>
+          <t>6515穎崴科技</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+5.47%810</t>
+          <t>-2.42%5850</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+5.47%</t>
+          <t>-2.42%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>810</v>
+        <v>5850</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.12%404,000</t>
+          <t>1.63%55,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.12%</t>
+          <t>1.63%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>404000</v>
+        <v>55000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2011,17 +2011,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-24 21:39:35</t>
+          <t>2026-09-24 21:47:16</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00980A/holdings</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -2029,34 +2029,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>3711日月光投控</t>
+          <t>6669緯穎科技服務</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+0.87%699</t>
+          <t>+0.48%2115</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+0.87%</t>
+          <t>+0.48%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>699</v>
+        <v>2115</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.11%464,000</t>
+          <t>1.62%155,105</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.62%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>464000</v>
+        <v>155105</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -2072,17 +2072,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-24 21:39:35</t>
+          <t>2026-09-24 21:47:16</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00980A/holdings</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -2090,38 +2090,38 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2303聯電</t>
+          <t>8046南亞電路板</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-3.75%154</t>
+          <t>+2.48%1240</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-3.75%</t>
+          <t>+2.48%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>154</v>
+        <v>1240</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.10%2,096,000</t>
+          <t>1.50%251,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>1.50%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>2096000</v>
+        <v>251000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2133,17 +2133,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-24 21:39:35</t>
+          <t>2026-09-24 21:47:16</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00980A/holdings</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -2151,38 +2151,38 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2449京元電子</t>
+          <t>3189景碩科技</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>+2.3%311</t>
+          <t>+6.18%962</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+2.3%</t>
+          <t>+6.18%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>311</v>
+        <v>962</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.06%999,000</t>
+          <t>1.45%323,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1.06%</t>
+          <t>1.45%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>999000</v>
+        <v>323000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2194,17 +2194,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-24 21:39:35</t>
+          <t>2026-09-24 21:47:16</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00980A/holdings</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -2212,12 +2212,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2603長榮</t>
+          <t>2884玉山金融控股</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0%243</t>
+          <t>0%45.6</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2226,20 +2226,20 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>243</v>
+        <v>45.6</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.97%1,169,000</t>
+          <t>1.43%6,340,622</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>1.43%</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>1169000</v>
+        <v>6340622</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2255,17 +2255,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-24 21:39:35</t>
+          <t>2026-09-24 21:47:16</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00980A/holdings</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -2273,38 +2273,38 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2313華通</t>
+          <t>2327國巨</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-0.67%222.5</t>
+          <t>+1.22%580</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-0.67%</t>
+          <t>+1.22%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>222.5</v>
+        <v>580</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.84%1,107,336</t>
+          <t>1.38%485,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>1.38%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>1107336</v>
+        <v>485000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2316,17 +2316,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-24 21:39:36</t>
+          <t>2026-09-24 21:47:17</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00980A/holdings</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -2334,38 +2334,38 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>3008大立光</t>
+          <t>8996高力熱處理工業</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+0.89%6245</t>
+          <t>-0.65%1530</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+0.89%</t>
+          <t>-0.65%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>6245</v>
+        <v>1530</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.83%39,000</t>
+          <t>1.38%181,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>1.38%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>39000</v>
+        <v>181000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2377,17 +2377,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-24 21:39:36</t>
+          <t>2026-09-24 21:47:17</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00980A/holdings</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -2395,38 +2395,38 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2317鴻海</t>
+          <t>6213聯茂電子</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-2.15%250.5</t>
+          <t>+9.98%595</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-2.15%</t>
+          <t>+9.98%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>250.5</v>
+        <v>595</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.82%960,000</t>
+          <t>1.29%482,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>1.29%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>960000</v>
+        <v>482000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2438,17 +2438,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-24 21:39:36</t>
+          <t>2026-09-24 21:47:17</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00980A/holdings</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -2456,38 +2456,38 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>7750新 代</t>
+          <t>2891中國信託金融控股</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>+1.03%1970</t>
+          <t>-0.58%68.5</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+1.03%</t>
+          <t>-0.58%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>1970</v>
+        <v>68.5</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.82%122,000</t>
+          <t>1.26%3,699,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>1.26%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>122000</v>
+        <v>3699000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2499,17 +2499,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-24 21:39:36</t>
+          <t>2026-09-24 21:47:17</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00980A/holdings</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -2517,38 +2517,38 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>3081聯 亞</t>
+          <t>2376技嘉科技</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+0.75%2700</t>
+          <t>-0.96%361.5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+0.75%</t>
+          <t>-0.96%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>2700</v>
+        <v>361.5</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.76%82,000</t>
+          <t>1.25%694,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.76%</t>
+          <t>1.25%</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>82000</v>
+        <v>694000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2560,17 +2560,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-24 21:39:36</t>
+          <t>2026-09-24 21:47:17</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00980A/holdings</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -2578,38 +2578,38 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>3374精 材</t>
+          <t>3036文曄科技</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-4.87%449</t>
+          <t>+0.49%207</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-4.87%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>449</v>
+        <v>207</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.52%340,000</t>
+          <t>1.17%1,147,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>1.17%</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>340000</v>
+        <v>1147000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2621,17 +2621,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-24 21:39:36</t>
+          <t>2026-09-24 21:47:17</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00980A/holdings</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -2639,38 +2639,38 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>3167大 量</t>
+          <t>3231緯創資通</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+6.63%949</t>
+          <t>+2.5%184.5</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+6.63%</t>
+          <t>+2.5%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>949</v>
+        <v>184.5</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.37%115,000</t>
+          <t>1.16%1,298,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>1.16%</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>115000</v>
+        <v>1298000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2682,17 +2682,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-24 21:39:36</t>
+          <t>2026-09-24 21:47:17</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00980A/holdings</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -2700,38 +2700,38 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>5434崇越</t>
+          <t>5904寶雅國際</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0%542</t>
+          <t>-2.12%69.3</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-2.12%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>542</v>
+        <v>69.3</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.37%200,000</t>
+          <t>1.10%3,124,500</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>1.10%</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>200000</v>
+        <v>3124500</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2743,17 +2743,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-24 21:39:36</t>
+          <t>2026-09-24 21:47:17</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00980A/holdings</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -2761,38 +2761,38 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>3293鈊 象</t>
+          <t>3026禾伸堂企業</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+4.39%761</t>
+          <t>+5.47%810</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+4.39%</t>
+          <t>+5.47%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>761</v>
+        <v>810</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.35%133,000</t>
+          <t>1.09%286,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>1.09%</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>133000</v>
+        <v>286000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2804,17 +2804,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-24 21:39:36</t>
+          <t>2026-09-24 21:47:17</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00980A/holdings</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -2822,38 +2822,38 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>3090日電貿</t>
+          <t>3044健鼎科技</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>0%165</t>
+          <t>-0.92%538</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-0.92%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>165</v>
+        <v>538</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.33%592,000</t>
+          <t>0.93%345,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.33%</t>
+          <t>0.93%</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>592000</v>
+        <v>345000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2865,17 +2865,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-24 21:39:36</t>
+          <t>2026-09-24 21:47:17</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00980A/holdings</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -2883,38 +2883,38 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>6442光 聖</t>
+          <t>3293鈊象電子</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+0.99%1530</t>
+          <t>+4.39%761</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+0.99%</t>
+          <t>+4.39%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1530</v>
+        <v>761</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.30%58,000</t>
+          <t>0.91%252,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.91%</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>58000</v>
+        <v>252000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2926,17 +2926,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-24 21:39:36</t>
+          <t>2026-09-24 21:47:17</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00980A/holdings</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -2944,38 +2944,38 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2637慧洋-KY</t>
+          <t>3264欣銓科技</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0%100.5</t>
+          <t>-2.38%246</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-2.38%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>100.5</v>
+        <v>246</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.29%834,000</t>
+          <t>0.81%650,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.81%</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>834000</v>
+        <v>650000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2987,17 +2987,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-24 21:39:36</t>
+          <t>2026-09-24 21:47:17</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00980A/holdings</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -3005,38 +3005,38 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>6271同欣電</t>
+          <t>3008大立光電</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+0.22%229</t>
+          <t>+0.89%6245</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+0.22%</t>
+          <t>+0.89%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>229</v>
+        <v>6245</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.27%340,000</t>
+          <t>0.80%26,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>0.80%</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>340000</v>
+        <v>26000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3048,17 +3048,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-24 21:39:36</t>
+          <t>2026-09-24 21:47:17</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00980A/holdings</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -3066,38 +3066,38 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>6121新 普</t>
+          <t>3529力旺電子</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-0.13%376</t>
+          <t>-2.27%3230</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>-2.27%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>376</v>
+        <v>3230</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.23%178,000</t>
+          <t>0.72%44,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.23%</t>
+          <t>0.72%</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>178000</v>
+        <v>44000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3109,17 +3109,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-24 21:39:36</t>
+          <t>2026-09-24 21:47:17</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00980A/holdings</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -3127,38 +3127,38 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>7769鴻 勁</t>
+          <t>4958臻鼎科技控股</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-5.1%5670</t>
+          <t>+0.53%475.5</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-5.1%</t>
+          <t>+0.53%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>5670</v>
+        <v>475.5</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.14%7,000</t>
+          <t>0.71%302,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.14%</t>
+          <t>0.71%</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>7000</v>
+        <v>302000</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3170,17 +3170,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-24 21:39:36</t>
+          <t>2026-09-24 21:47:17</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00980A/holdings</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -3188,41 +3188,3091 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
+          <t>6805富世達</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>-2.69%2530</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-2.69%</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>2530</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>0.70%54,000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>0.70%</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>54000</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>-0.02%</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>00980A</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-09-24 21:47:18</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00980A/holdings</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>4</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>3665貿聯控股（BizLink Holding In</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0%2340</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>2340</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.56%48,336</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.56%</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
+        <v>48336</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>00980A</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-09-24 21:47:18</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00980A/holdings</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>4</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>6831邁科科技</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>-3.4%497.5</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-3.4%</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>497.5</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.46%182,000</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.46%</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
+        <v>182000</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>-0.02%</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>00980A</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-09-24 21:47:18</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00980A/holdings</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>4</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>8210勤誠興業</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>+0.56%897</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>+0.56%</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>897</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.42%95,000</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.42%</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>95000</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>00980A</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-09-24 21:47:18</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00980A/holdings</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>4</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>6442光紅建聖</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>+0.99%1530</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>+0.99%</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>1530</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.29%38,000</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.29%</t>
+        </is>
+      </c>
+      <c r="K50" t="n">
+        <v>38000</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>00980A</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-09-24 21:47:18</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00980A/holdings</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>4</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>3533嘉澤端子工業</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0%1690</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>1690</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.29%35,000</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.29%</t>
+        </is>
+      </c>
+      <c r="K51" t="n">
+        <v>35000</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-09-24 21:48:24</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>2330台積電</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>-1%2475</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-1%</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>2475</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>8.75%1,034,000</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>8.75%</t>
+        </is>
+      </c>
+      <c r="K52" t="n">
+        <v>1034000</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>-0.09%</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-09-24 21:48:24</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2454聯發科</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>+1.93%5285</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>+1.93%</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>5285</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>7.99%442,000</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>7.99%</t>
+        </is>
+      </c>
+      <c r="K53" t="n">
+        <v>442000</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>+0.15%</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-09-24 21:48:24</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>3653健策</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>+7.96%6920</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>+7.96%</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>6920</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>5.23%221,000</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>5.23%</t>
+        </is>
+      </c>
+      <c r="K54" t="n">
+        <v>221000</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>+0.39%</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-09-24 21:48:24</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2059川湖</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>-0.32%12350</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>-0.32%</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>12350</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>5.19%123,000</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>5.19%</t>
+        </is>
+      </c>
+      <c r="K55" t="n">
+        <v>123000</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>-0.02%</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-09-24 21:48:24</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>3443創意</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>+1.67%8525</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>+1.67%</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>8525</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>5.04%173,000</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>5.04%</t>
+        </is>
+      </c>
+      <c r="K56" t="n">
+        <v>173000</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>+0.08%</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-09-24 21:48:24</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>3037欣興</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>+2.16%1185</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>+2.16%</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>1185</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>4.90%1,209,000</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>4.90%</t>
+        </is>
+      </c>
+      <c r="K57" t="n">
+        <v>1209000</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>+0.10%</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-09-24 21:48:24</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>3017奇鋐</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>+2.45%3555</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>+2.45%</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>3555</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>4.58%377,000</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>4.58%</t>
+        </is>
+      </c>
+      <c r="K58" t="n">
+        <v>377000</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>+0.11%</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-09-24 21:48:24</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>6223旺矽</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>-3.65%5415</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>-3.65%</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>5415</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>4.41%238,000</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>4.41%</t>
+        </is>
+      </c>
+      <c r="K59" t="n">
+        <v>238000</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>-0.17%</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-09-24 21:48:24</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>2383台光電</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>+0.6%5050</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>+0.6%</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>5050</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>3.92%227,000</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>3.92%</t>
+        </is>
+      </c>
+      <c r="K60" t="n">
+        <v>227000</v>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>+0.02%</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-09-24 21:48:24</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>2308台達電</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>+0.53%1910</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>+0.53%</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>1910</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>3.91%598,000</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>3.91%</t>
+        </is>
+      </c>
+      <c r="K61" t="n">
+        <v>598000</v>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>+0.02%</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-09-24 21:48:24</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>2360致茂</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>-1.29%2295</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>-1.29%</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>2295</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>3.69%470,000</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>3.69%</t>
+        </is>
+      </c>
+      <c r="K62" t="n">
+        <v>470000</v>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>-0.05%</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-09-24 21:48:24</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>5274信 驊</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>-2.19%19835</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>-2.19%</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>19835</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>3.21%47,400</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>3.21%</t>
+        </is>
+      </c>
+      <c r="K63" t="n">
+        <v>47400</v>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>-0.07%</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-09-24 21:48:24</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>6669緯穎</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>+0.48%2115</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>+0.48%</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>2115</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>3.17%438,197</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>3.17%</t>
+        </is>
+      </c>
+      <c r="K64" t="n">
+        <v>438197</v>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>+0.02%</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-09-24 21:48:24</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>1303南亞</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>+4.62%238</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>+4.62%</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>238</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>2.95%3,627,000</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>2.95%</t>
+        </is>
+      </c>
+      <c r="K65" t="n">
+        <v>3627000</v>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>+0.13%</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-09-24 21:48:24</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>6187萬 潤</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>-0.83%1195</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>-0.83%</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>1195</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>2.44%596,000</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>2.44%</t>
+        </is>
+      </c>
+      <c r="K66" t="n">
+        <v>596000</v>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>-0.02%</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-09-24 21:48:25</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>2</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>6488環球晶</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>-0.21%948</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>-0.21%</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>948</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>2.02%622,000</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>2.02%</t>
+        </is>
+      </c>
+      <c r="K67" t="n">
+        <v>622000</v>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-09-24 21:48:25</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>2</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>3665貿聯-KY</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>0%2340</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
+        <v>2340</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1.93%241,000</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>1.93%</t>
+        </is>
+      </c>
+      <c r="K68" t="n">
+        <v>241000</v>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-09-24 21:48:25</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>2</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>3044健鼎</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>-0.92%538</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>-0.92%</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
+        <v>538</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1.90%1,034,000</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>1.90%</t>
+        </is>
+      </c>
+      <c r="K69" t="n">
+        <v>1034000</v>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>-0.02%</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-09-24 21:48:25</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>2</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>2881富邦金</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>-1.96%150</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>-1.96%</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
+        <v>150</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1.59%3,104,000</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>1.59%</t>
+        </is>
+      </c>
+      <c r="K70" t="n">
+        <v>3104000</v>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>-0.03%</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-09-24 21:48:25</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>2</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>3036文曄</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>+0.49%207</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>+0.49%</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
+        <v>207</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1.56%2,208,000</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>1.56%</t>
+        </is>
+      </c>
+      <c r="K71" t="n">
+        <v>2208000</v>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-09-24 21:48:25</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>2</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>2345智邦</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>+0.26%1895</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>+0.26%</t>
+        </is>
+      </c>
+      <c r="H72" t="n">
+        <v>1895</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1.47%227,000</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>1.47%</t>
+        </is>
+      </c>
+      <c r="K72" t="n">
+        <v>227000</v>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026-09-24 21:48:25</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>2</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>6505台塑化</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>-0.11%87.2</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>-0.11%</t>
+        </is>
+      </c>
+      <c r="H73" t="n">
+        <v>87.2</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1.46%4,903,000</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>1.46%</t>
+        </is>
+      </c>
+      <c r="K73" t="n">
+        <v>4903000</v>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2026-09-24 21:48:25</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>2</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>3529力旺</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>-2.27%3230</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>-2.27%</t>
+        </is>
+      </c>
+      <c r="H74" t="n">
+        <v>3230</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1.46%132,000</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>1.46%</t>
+        </is>
+      </c>
+      <c r="K74" t="n">
+        <v>132000</v>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>-0.03%</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2026-09-24 21:48:25</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>2</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>2368金像電</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>-3.07%1105</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>-3.07%</t>
+        </is>
+      </c>
+      <c r="H75" t="n">
+        <v>1105</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>1.43%378,000</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>1.43%</t>
+        </is>
+      </c>
+      <c r="K75" t="n">
+        <v>378000</v>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>-0.05%</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2026-09-24 21:48:25</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>2</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>3026禾伸堂</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>+5.47%810</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>+5.47%</t>
+        </is>
+      </c>
+      <c r="H76" t="n">
+        <v>810</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1.12%404,000</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>1.12%</t>
+        </is>
+      </c>
+      <c r="K76" t="n">
+        <v>404000</v>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>+0.06%</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2026-09-24 21:48:25</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>2</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>3711日月光投控</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>+0.87%699</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>+0.87%</t>
+        </is>
+      </c>
+      <c r="H77" t="n">
+        <v>699</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1.11%464,000</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>1.11%</t>
+        </is>
+      </c>
+      <c r="K77" t="n">
+        <v>464000</v>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2026-09-24 21:48:25</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>2</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>2303聯電</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>-3.75%154</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>-3.75%</t>
+        </is>
+      </c>
+      <c r="H78" t="n">
+        <v>154</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>1.10%2,096,000</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>1.10%</t>
+        </is>
+      </c>
+      <c r="K78" t="n">
+        <v>2096000</v>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>-0.04%</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026-09-24 21:48:25</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>2</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>2449京元電子</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>+2.3%311</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>+2.3%</t>
+        </is>
+      </c>
+      <c r="H79" t="n">
+        <v>311</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1.06%999,000</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>1.06%</t>
+        </is>
+      </c>
+      <c r="K79" t="n">
+        <v>999000</v>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>+0.02%</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026-09-24 21:48:25</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>2</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>2603長榮</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>0%243</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="H80" t="n">
+        <v>243</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>0.97%1,169,000</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>0.97%</t>
+        </is>
+      </c>
+      <c r="K80" t="n">
+        <v>1169000</v>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2026-09-24 21:48:25</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>2</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>2313華通</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>-0.67%222.5</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>-0.67%</t>
+        </is>
+      </c>
+      <c r="H81" t="n">
+        <v>222.5</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>0.84%1,107,336</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>0.84%</t>
+        </is>
+      </c>
+      <c r="K81" t="n">
+        <v>1107336</v>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2026-09-24 21:48:27</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>3</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>3008大立光</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>+0.89%6245</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>+0.89%</t>
+        </is>
+      </c>
+      <c r="H82" t="n">
+        <v>6245</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>0.83%39,000</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>0.83%</t>
+        </is>
+      </c>
+      <c r="K82" t="n">
+        <v>39000</v>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2026-09-24 21:48:27</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>3</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>2317鴻海</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>-2.15%250.5</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>-2.15%</t>
+        </is>
+      </c>
+      <c r="H83" t="n">
+        <v>250.5</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>0.82%960,000</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>0.82%</t>
+        </is>
+      </c>
+      <c r="K83" t="n">
+        <v>960000</v>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>-0.02%</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026-09-24 21:48:27</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>3</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>7750新 代</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>+1.03%1970</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>+1.03%</t>
+        </is>
+      </c>
+      <c r="H84" t="n">
+        <v>1970</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>0.82%122,000</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>0.82%</t>
+        </is>
+      </c>
+      <c r="K84" t="n">
+        <v>122000</v>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026-09-24 21:48:27</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>3</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>3081聯 亞</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>+0.75%2700</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>+0.75%</t>
+        </is>
+      </c>
+      <c r="H85" t="n">
+        <v>2700</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>0.76%82,000</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>0.76%</t>
+        </is>
+      </c>
+      <c r="K85" t="n">
+        <v>82000</v>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026-09-24 21:48:27</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>3</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>3374精 材</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>-4.87%449</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>-4.87%</t>
+        </is>
+      </c>
+      <c r="H86" t="n">
+        <v>449</v>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>0.52%340,000</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>0.52%</t>
+        </is>
+      </c>
+      <c r="K86" t="n">
+        <v>340000</v>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>-0.03%</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2026-09-24 21:48:27</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>3</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>3167大 量</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>+6.63%949</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>+6.63%</t>
+        </is>
+      </c>
+      <c r="H87" t="n">
+        <v>949</v>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>0.37%115,000</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>0.37%</t>
+        </is>
+      </c>
+      <c r="K87" t="n">
+        <v>115000</v>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>+0.02%</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2026-09-24 21:48:27</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>3</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>5434崇越</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>0%542</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="H88" t="n">
+        <v>542</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>0.37%200,000</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>0.37%</t>
+        </is>
+      </c>
+      <c r="K88" t="n">
+        <v>200000</v>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2026-09-24 21:48:27</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>3</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>3293鈊 象</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>+4.39%761</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>+4.39%</t>
+        </is>
+      </c>
+      <c r="H89" t="n">
+        <v>761</v>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>0.35%133,000</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>0.35%</t>
+        </is>
+      </c>
+      <c r="K89" t="n">
+        <v>133000</v>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2026-09-24 21:48:27</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>3</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>3090日電貿</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>0%165</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="H90" t="n">
+        <v>165</v>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>0.33%592,000</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>0.33%</t>
+        </is>
+      </c>
+      <c r="K90" t="n">
+        <v>592000</v>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2026-09-24 21:48:27</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>3</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>6442光 聖</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>+0.99%1530</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>+0.99%</t>
+        </is>
+      </c>
+      <c r="H91" t="n">
+        <v>1530</v>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>0.30%58,000</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>0.30%</t>
+        </is>
+      </c>
+      <c r="K91" t="n">
+        <v>58000</v>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2026-09-24 21:48:27</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>3</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>2637慧洋-KY</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>0%100.5</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="H92" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>0.29%834,000</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>0.29%</t>
+        </is>
+      </c>
+      <c r="K92" t="n">
+        <v>834000</v>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2026-09-24 21:48:27</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>3</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>6271同欣電</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>+0.22%229</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>+0.22%</t>
+        </is>
+      </c>
+      <c r="H93" t="n">
+        <v>229</v>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>0.27%340,000</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>0.27%</t>
+        </is>
+      </c>
+      <c r="K93" t="n">
+        <v>340000</v>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2026-09-24 21:48:27</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>3</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>6121新 普</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>-0.13%376</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>-0.13%</t>
+        </is>
+      </c>
+      <c r="H94" t="n">
+        <v>376</v>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>0.23%178,000</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>0.23%</t>
+        </is>
+      </c>
+      <c r="K94" t="n">
+        <v>178000</v>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2026-09-24 21:48:27</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>3</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>7769鴻 勁</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>-5.1%5670</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>-5.1%</t>
+        </is>
+      </c>
+      <c r="H95" t="n">
+        <v>5670</v>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>0.14%7,000</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>0.14%</t>
+        </is>
+      </c>
+      <c r="K95" t="n">
+        <v>7000</v>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2026-09-24 21:48:27</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>3</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
           <t>9939宏全</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F96" t="inlineStr">
         <is>
           <t>-0.4%124.5</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G96" t="inlineStr">
         <is>
           <t>-0.4%</t>
         </is>
       </c>
-      <c r="H46" t="n">
+      <c r="H96" t="n">
         <v>124.5</v>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="I96" t="inlineStr">
         <is>
           <t>0.08%180,000</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="J96" t="inlineStr">
         <is>
           <t>0.08%</t>
         </is>
       </c>
-      <c r="K46" t="n">
+      <c r="K96" t="n">
         <v>180000</v>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="L96" t="inlineStr">
         <is>
           <t>-0.00%</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="M96" t="inlineStr">
         <is>
           <t>登入查看</t>
         </is>
